--- a/skill/activeskill.xlsx
+++ b/skill/activeskill.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>ID</t>
   </si>
@@ -41,12 +41,6 @@
   </si>
   <si>
     <t>describe</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
   </si>
   <si>
     <t>破晓</t>
@@ -1128,7 +1122,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="12.5555555555556" customWidth="1"/>
@@ -1150,136 +1144,122 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" t="s">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
-      <c r="A10">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" t="s">
-        <v>29</v>
-      </c>
+    <row r="10" spans="3:3">
+      <c r="C10" s="1"/>
     </row>
     <row r="11" spans="3:3">
       <c r="C11" s="1"/>
-    </row>
-    <row r="12" spans="3:3">
-      <c r="C12" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/skill/activeskill.xlsx
+++ b/skill/activeskill.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>ID</t>
   </si>
@@ -41,6 +41,15 @@
   </si>
   <si>
     <t>describe</t>
+  </si>
+  <si>
+    <t>power</t>
+  </si>
+  <si>
+    <t>config</t>
+  </si>
+  <si>
+    <t>cd</t>
   </si>
   <si>
     <t>破晓</t>
@@ -1122,14 +1131,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="12.5555555555556" customWidth="1"/>
     <col min="3" max="3" width="26.8888888888889" customWidth="1"/>
+    <col min="4" max="4" width="44.1111111111111" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1142,117 +1152,186 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>12</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>15</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>18</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>21</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>27</v>
+      </c>
+      <c r="E8">
+        <v>3</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
+        <v>30</v>
+      </c>
+      <c r="E9">
+        <v>3</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="3:3">
